--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104471_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104471_W2.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5563</v>
+        <v>5.4869</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0818</v>
+        <v>3.9516</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4746</v>
+        <v>1.5352</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2886</v>
+        <v>3.2927</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2756</v>
+        <v>2.272</v>
       </c>
       <c r="I2" t="n">
-        <v>1.013</v>
+        <v>1.0207</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6616</v>
+        <v>1.6406</v>
       </c>
       <c r="K2" t="n">
-        <v>1.475</v>
+        <v>1.4544</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M2" t="n">
-        <v>1.6269</v>
+        <v>1.6522</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8006</v>
+        <v>0.8176</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6396</v>
+        <v>-0.7164</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7652</v>
+        <v>0.1321</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8744</v>
+        <v>-0.8485</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4509</v>
+        <v>3.9162</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4501</v>
+        <v>0.7322</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0008</v>
+        <v>3.1841</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5073</v>
+        <v>4.5233</v>
       </c>
       <c r="H3" t="n">
-        <v>3.473</v>
+        <v>3.4833</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0343</v>
+        <v>1.04</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8463</v>
+        <v>1.8382</v>
       </c>
       <c r="K3" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M3" t="n">
-        <v>2.661</v>
+        <v>2.6851</v>
       </c>
       <c r="N3" t="n">
-        <v>1.776</v>
+        <v>1.7941</v>
       </c>
       <c r="O3" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5762</v>
+        <v>-1.1322</v>
       </c>
       <c r="T3" t="n">
-        <v>0.738</v>
+        <v>0.0322</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3141</v>
+        <v>-1.1644</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. GOLDEN</t>
+          <t>D. PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1956</v>
+        <v>2.9962</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5177</v>
+        <v>-0.35</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7133</v>
+        <v>3.3462</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7504999999999999</v>
+        <v>3.7357</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1957</v>
+        <v>1.4386</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4452</v>
+        <v>2.2971</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7144</v>
+        <v>1.6258</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8636</v>
+        <v>0.4342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1493</v>
+        <v>1.1916</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0362</v>
+        <v>2.1099</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3321</v>
+        <v>1.0044</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2959</v>
+        <v>1.1055</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6512</v>
+        <v>-0.2159</v>
       </c>
       <c r="T4" t="n">
-        <v>2.102</v>
+        <v>-0.2442</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5492</v>
+        <v>0.0283</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7712</v>
+        <v>0.5447</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3856</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. PEREZ</t>
+          <t>R. OBASOHAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1512</v>
+        <v>2.5796</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9195</v>
+        <v>1.5644</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0706</v>
+        <v>1.0151</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7278</v>
+        <v>4.0859</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4328</v>
+        <v>3.0099</v>
       </c>
       <c r="I5" t="n">
-        <v>2.295</v>
+        <v>1.0759</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6373</v>
+        <v>2.6902</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4431</v>
+        <v>2.02</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1941</v>
+        <v>0.6703</v>
       </c>
       <c r="M5" t="n">
-        <v>2.0905</v>
+        <v>1.3956</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9896</v>
+        <v>0.99</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1009</v>
+        <v>0.4057</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0549</v>
+        <v>-1.9812</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8347</v>
+        <v>-0.6415</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2202</v>
+        <v>-1.3397</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3856</v>
+        <v>0.7025</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5463</v>
+        <v>1.792</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0382</v>
+        <v>2.0972</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2361</v>
+        <v>0.0442</v>
       </c>
       <c r="F6" t="n">
-        <v>1.802</v>
+        <v>2.053</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9435</v>
+        <v>1.9496</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3331</v>
+        <v>1.3436</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6061</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9801</v>
+        <v>0.9552</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3912</v>
+        <v>0.3825</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5889</v>
+        <v>0.5728</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9634</v>
+        <v>0.9944</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9419</v>
+        <v>0.9611</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4932</v>
+        <v>-1.4458</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.744</v>
+        <v>-0.911</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7492</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. OBASOHAN</t>
+          <t>H. BENITEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7982</v>
+        <v>1.6786</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1264</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6718</v>
+        <v>2.4472</v>
       </c>
       <c r="G7" t="n">
-        <v>4.0763</v>
+        <v>2.562</v>
       </c>
       <c r="H7" t="n">
-        <v>3.01</v>
+        <v>-0.4426</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0663</v>
+        <v>3.0046</v>
       </c>
       <c r="J7" t="n">
-        <v>2.708</v>
+        <v>0.8229</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0363</v>
+        <v>-1.4037</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6717</v>
+        <v>2.2265</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3683</v>
+        <v>1.7391</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9737</v>
+        <v>0.9611</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3946</v>
+        <v>0.778</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.7583</v>
+        <v>-1.6362</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.113</v>
+        <v>-0.4533</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.6453</v>
+        <v>-1.1829</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7071</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. BENITEZ</t>
+          <t>A. PLUMMER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1084</v>
+        <v>0.8842</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4002</v>
+        <v>1.4451</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5086</v>
+        <v>-0.5609</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5567</v>
+        <v>1.8714</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4474</v>
+        <v>-0.273</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0041</v>
+        <v>2.1444</v>
       </c>
       <c r="J8" t="n">
-        <v>0.847</v>
+        <v>2.213</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3893</v>
+        <v>-0.6313</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2363</v>
+        <v>2.8442</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7097</v>
+        <v>-0.3416</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9419</v>
+        <v>0.3583</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7678</v>
+        <v>-0.6998</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.1948</v>
+        <v>-0.2148</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.113</v>
+        <v>-0.1745</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0819</v>
+        <v>-0.0403</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PLUMMER</t>
+          <t>G. GOLDEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1499</v>
+        <v>0.3396</v>
       </c>
       <c r="E9" t="n">
-        <v>0.892</v>
+        <v>-2.2164</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7421</v>
+        <v>2.556</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8833</v>
+        <v>-0.7716</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2756</v>
+        <v>-1.2248</v>
       </c>
       <c r="I9" t="n">
-        <v>2.159</v>
+        <v>0.4532</v>
       </c>
       <c r="J9" t="n">
-        <v>2.245</v>
+        <v>-0.7591</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6203</v>
+        <v>-0.908</v>
       </c>
       <c r="L9" t="n">
-        <v>2.8653</v>
+        <v>0.1489</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3617</v>
+        <v>-0.0125</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3446</v>
+        <v>-0.3168</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7063</v>
+        <v>0.3043</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9603</v>
+        <v>0.8152</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7652</v>
+        <v>0.4548</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1951</v>
+        <v>0.3605</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5463</v>
+        <v>-0.387</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5463</v>
+        <v>-0.7739</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0488</v>
+        <v>-0.5939</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7996</v>
+        <v>-2.1827</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7508</v>
+        <v>1.5888</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.846</v>
+        <v>-0.8496</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2698</v>
+        <v>-1.2695</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4238</v>
+        <v>0.4199</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7048</v>
+        <v>-2.7306</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.4008</v>
+        <v>-2.4174</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8587</v>
+        <v>1.881</v>
       </c>
       <c r="N10" t="n">
-        <v>1.131</v>
+        <v>1.1479</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3436</v>
+        <v>-0.1996</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9467</v>
+        <v>0.5966</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6031</v>
+        <v>-0.7962</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8407</v>
+        <v>-0.8607</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3478</v>
+        <v>-0.2788</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4929</v>
+        <v>-0.5819</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.149</v>
+        <v>-0.1419</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.149</v>
+        <v>-0.1419</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6917</v>
+        <v>-0.7188</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3478</v>
+        <v>-0.2788</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3439</v>
+        <v>-0.44</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>M. GASPA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.735</v>
+        <v>-1.8585</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6324</v>
+        <v>-1.4207</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8974</v>
+        <v>-0.4378</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7625</v>
+        <v>-0.6983</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9609</v>
+        <v>0.103</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.7234</v>
+        <v>-0.8012</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.2163</v>
+        <v>-0.7724</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1763</v>
+        <v>-0.7724</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.3926</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4538</v>
+        <v>0.0741</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7847</v>
+        <v>0.8754</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6691</v>
+        <v>-0.8012</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2543</v>
+        <v>-1.3878</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5353</v>
+        <v>-0.6483</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7896</v>
+        <v>-0.7396</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. GASPA</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1474</v>
+        <v>-2.6441</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6038</v>
+        <v>-5.9167</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5436</v>
+        <v>3.2726</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7099</v>
+        <v>-3.7744</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0951</v>
+        <v>0.9648</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.805</v>
+        <v>-4.7392</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.769</v>
+        <v>-5.2541</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.769</v>
+        <v>0.1616</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-5.4158</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0592</v>
+        <v>1.4798</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8641</v>
+        <v>0.8032</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.805</v>
+        <v>0.6766</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6643</v>
+        <v>-0.6421</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8347</v>
+        <v>-0.7716</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8296</v>
+        <v>0.1295</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.6768</v>
+        <v>14.0213</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.434599999999999</v>
+        <v>-5.396400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>19.1113</v>
+        <v>19.4176</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7656</v>
+        <v>15.7848</v>
       </c>
       <c r="H14" t="n">
-        <v>9.674799999999999</v>
+        <v>9.692300000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>6.0909</v>
+        <v>6.092599999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.520800000000001</v>
+        <v>2.269700000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1759000000000006</v>
+        <v>0.009100000000000358</v>
       </c>
       <c r="L14" t="n">
-        <v>2.345</v>
+        <v>2.2604</v>
       </c>
       <c r="M14" t="n">
-        <v>13.2446</v>
+        <v>13.5152</v>
       </c>
       <c r="N14" t="n">
-        <v>9.498799999999999</v>
+        <v>9.683299999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>3.7457</v>
+        <v>3.8322</v>
       </c>
       <c r="P14" t="n">
-        <v>5.6709</v>
+        <v>5.6909</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.3418</v>
+        <v>-11.3818</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.784199999999998</v>
+        <v>-9.4756</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.2662</v>
+        <v>-2.9075</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.518</v>
+        <v>-6.5681</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0248</v>
+        <v>2.0212</v>
       </c>
       <c r="W14" t="n">
-        <v>6.6525</v>
+        <v>6.623100000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.628</v>
+        <v>-4.6022</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>B. BURJANADZE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6831</v>
+        <v>2.2403</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1807</v>
+        <v>0.0696</v>
       </c>
       <c r="F15" t="n">
-        <v>3.8638</v>
+        <v>2.1707</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0628</v>
+        <v>1.2184</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7375</v>
+        <v>-0.7552</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3253</v>
+        <v>1.9736</v>
       </c>
       <c r="J15" t="n">
-        <v>0.643</v>
+        <v>0.6008</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4565</v>
+        <v>-0.9555</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1866</v>
+        <v>1.5563</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4197</v>
+        <v>0.6176</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2811</v>
+        <v>0.2003</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1387</v>
+        <v>0.4173</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0415</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8226</v>
+        <v>0.3194</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5788</v>
+        <v>0.1321</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2438</v>
+        <v>0.1873</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. BURJANADZE</t>
+          <t>M. THOMAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8663</v>
+        <v>1.1243</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2522</v>
+        <v>0.2815</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1185</v>
+        <v>0.8428</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2261</v>
+        <v>-0.2238</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7517</v>
+        <v>-2.2436</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9778</v>
+        <v>2.0198</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.3752</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9391</v>
+        <v>-2.1416</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5646</v>
+        <v>2.5168</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6006</v>
+        <v>-0.599</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1874</v>
+        <v>-0.102</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4132</v>
+        <v>-0.497</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0668</v>
+        <v>0.1903</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2238</v>
+        <v>0.0249</v>
       </c>
       <c r="U16" t="n">
-        <v>0.157</v>
+        <v>0.1655</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7071</v>
+        <v>1.2472</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. THOMAS</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0359</v>
+        <v>0.7127</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6758</v>
+        <v>-2.2795</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3601</v>
+        <v>2.9922</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2295</v>
+        <v>1.0597</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2526</v>
+        <v>0.7272</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0231</v>
+        <v>0.3325</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4084</v>
+        <v>0.6129</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.1237</v>
+        <v>0.4267</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5321</v>
+        <v>0.1862</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6379</v>
+        <v>0.4468</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1289</v>
+        <v>0.3005</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.509</v>
+        <v>0.1463</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1047</v>
+        <v>1.8594</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3751</v>
+        <v>0.522</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2704</v>
+        <v>1.3374</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7071</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>E. DURAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.6617</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7963</v>
+        <v>0.2239</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2152</v>
+        <v>0.4378</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1884</v>
+        <v>0.3331</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4806</v>
+        <v>0.1752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.669</v>
+        <v>0.1579</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1097</v>
+        <v>0.0172</v>
       </c>
       <c r="K18" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0172</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2981</v>
+        <v>0.3159</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4082</v>
+        <v>0.1579</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7063</v>
+        <v>0.1579</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5427</v>
+        <v>0.3287</v>
       </c>
       <c r="T18" t="n">
-        <v>2.0476</v>
+        <v>0.2067</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4951</v>
+        <v>0.122</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. DURAN</t>
+          <t>E. VALTONEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.51</v>
+        <v>0.0766</v>
       </c>
       <c r="E19" t="n">
-        <v>0.105</v>
+        <v>-0.0067</v>
       </c>
       <c r="F19" t="n">
-        <v>0.405</v>
+        <v>0.0833</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3319</v>
+        <v>-0.7593</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1746</v>
+        <v>1.8895</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1573</v>
+        <v>-2.6489</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0173</v>
+        <v>-0.2033</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0173</v>
+        <v>1.6892</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.8925</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3145</v>
+        <v>-0.556</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1573</v>
+        <v>0.2003</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1573</v>
+        <v>-0.7563</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1781</v>
+        <v>1.4505</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0877</v>
+        <v>1.2469</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.2036</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. VALTONEN</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4605</v>
+        <v>0.046</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3747</v>
+        <v>-1.7221</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0857</v>
+        <v>1.7681</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7572</v>
+        <v>0.4385</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8844</v>
+        <v>0.2124</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6416</v>
+        <v>0.226</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1796</v>
+        <v>-0.4834</v>
       </c>
       <c r="K20" t="n">
-        <v>1.697</v>
+        <v>-1.0934</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8767</v>
+        <v>0.61</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5776</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1874</v>
+        <v>1.3058</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7649</v>
+        <v>-0.384</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.5934</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8301</v>
+        <v>0.3995</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5939</v>
+        <v>0.1969</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2362</v>
+        <v>0.2025</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3856</v>
+        <v>-1.2472</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3214</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7071</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9849</v>
+        <v>-0.725</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2747</v>
+        <v>-1.5185</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2898</v>
+        <v>0.7935</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4451</v>
+        <v>-2.6596</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2106</v>
+        <v>-0.6694</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2345</v>
+        <v>-1.9902</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4514</v>
+        <v>-1.9152</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0776</v>
+        <v>-0.4104</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6263</v>
+        <v>-1.5048</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8965</v>
+        <v>-0.7444</v>
       </c>
       <c r="N21" t="n">
-        <v>1.2883</v>
+        <v>-0.259</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3918</v>
+        <v>-0.4854</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6303</v>
+        <v>1.2517</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3962</v>
+        <v>0.852</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2341</v>
+        <v>0.3997</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2149</v>
+        <v>-0.9307</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8641</v>
+        <v>-0.5158</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6492</v>
+        <v>-0.4149</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6624</v>
+        <v>-0.1884</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6739000000000001</v>
+        <v>0.4742</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9885</v>
+        <v>-0.6626</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9035</v>
+        <v>0.0955</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4054</v>
+        <v>0.0582</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4981</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.759</v>
+        <v>-0.2838</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2685</v>
+        <v>0.416</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4904</v>
+        <v>-0.6998</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>0.767</v>
+        <v>1.0301</v>
       </c>
       <c r="T22" t="n">
-        <v>0.493</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.274</v>
+        <v>0.2755</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. AURRECOECHEA</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2398</v>
+        <v>-0.9901</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2653</v>
+        <v>0.0733</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5051</v>
+        <v>-1.0635</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2217</v>
+        <v>-2.8191</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3203</v>
+        <v>-1.2718</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09859999999999999</v>
+        <v>-1.5473</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.769</v>
+        <v>-1.5752</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.769</v>
+        <v>-0.8973</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4526</v>
+        <v>-1.2439</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5513</v>
+        <v>-0.3745</v>
       </c>
       <c r="O23" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.8694</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>2.2088</v>
+        <v>1.1461</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3954</v>
+        <v>0.7867</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1866</v>
+        <v>0.3594</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>I. AURRECOECHEA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9797</v>
+        <v>-2.3868</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7206</v>
+        <v>-0.7982</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2591</v>
+        <v>-1.5885</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.819</v>
+        <v>-1.217</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2624</v>
+        <v>-1.3184</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5566</v>
+        <v>0.1014</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5411</v>
+        <v>-0.7724</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8667</v>
+        <v>-0.7724</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6744</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2779</v>
+        <v>-0.4446</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3957</v>
+        <v>-0.546</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8822</v>
+        <v>0.1014</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1588</v>
+        <v>1.0579</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0453</v>
+        <v>1.34</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2041</v>
+        <v>-0.2821</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.2719</v>
+        <v>-5.3338</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.964</v>
+        <v>-6.8295</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6922</v>
+        <v>1.4957</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.4189</v>
+        <v>-5.4349</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.3158</v>
+        <v>-3.3253</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.1032</v>
+        <v>-2.1096</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.4436</v>
+        <v>-6.483</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.2982</v>
+        <v>-3.3244</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.1454</v>
+        <v>-3.1586</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0247</v>
+        <v>1.0481</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0176</v>
+        <v>-0.0009</v>
       </c>
       <c r="O25" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.131</v>
+        <v>0.8327</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3448</v>
+        <v>0.8403</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2138</v>
+        <v>-0.0077</v>
       </c>
       <c r="V25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.1225</v>
+        <v>-8.049300000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.0721</v>
+        <v>-6.277</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.0504</v>
+        <v>-1.7723</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.5342</v>
+        <v>-5.5324</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.5857</v>
+        <v>-3.5871</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.9485</v>
+        <v>-1.9453</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.7604</v>
+        <v>-3.7843</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.2623</v>
+        <v>-2.2795</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.7738</v>
+        <v>-1.7481</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.3234</v>
+        <v>-1.3077</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0005</v>
+        <v>0.0765</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0434</v>
+        <v>-0.2164</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0429</v>
+        <v>0.2929</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-13.6768</v>
+        <v>-13.5541</v>
       </c>
       <c r="E27" t="n">
-        <v>-19.1113</v>
+        <v>-19.299</v>
       </c>
       <c r="F27" t="n">
-        <v>5.4345</v>
+        <v>5.744900000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>-15.7654</v>
+        <v>-15.7848</v>
       </c>
       <c r="H27" t="n">
-        <v>-9.674700000000001</v>
+        <v>-9.692299999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-6.090800000000001</v>
+        <v>-6.092699999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>-13.2447</v>
+        <v>-13.5152</v>
       </c>
       <c r="K27" t="n">
-        <v>-9.498799999999999</v>
+        <v>-9.683199999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.7458</v>
+        <v>-3.832099999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.5209</v>
+        <v>-2.2695</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.1756999999999995</v>
+        <v>-0.009299999999999864</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.3449</v>
+        <v>-2.2605</v>
       </c>
       <c r="P27" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="Q27" t="n">
-        <v>-17.0124</v>
+        <v>-17.0724</v>
       </c>
       <c r="R27" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S27" t="n">
-        <v>9.784199999999998</v>
+        <v>9.942799999999998</v>
       </c>
       <c r="T27" t="n">
-        <v>6.517999999999999</v>
+        <v>6.686599999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>3.2662</v>
+        <v>3.256000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.0245</v>
+        <v>-2.0212</v>
       </c>
       <c r="W27" t="n">
-        <v>4.628</v>
+        <v>4.602</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.6526</v>
+        <v>-6.6232</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104471_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104471_W2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-4.6022</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104471_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.6232</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
